--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047BEA4C-625B-4A75-80AA-1A23132AD90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18573534-4261-4137-81B5-1237E39F8BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1442,69 +1442,135 @@
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>100</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>760</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>680</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>60</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>100</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>250</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18573534-4261-4137-81B5-1237E39F8BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B485B08-C0A4-4A99-AD2E-DD221968CB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Neutral</t>
   </si>
 </sst>
 </file>
@@ -871,7 +874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1025,11 +1028,11 @@
         <v>60</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1070</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>370</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1574,443 +1577,883 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>100</v>
+      </c>
+      <c r="E19" s="14">
+        <v>30</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>100</v>
+      </c>
+      <c r="E20" s="14">
+        <v>30</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
+        <v>100</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="14">
+        <v>480</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>180</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>180</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>0</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>180</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>0</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>720</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>100</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>100</v>
+      </c>
+      <c r="E27" s="14">
+        <v>40</v>
+      </c>
+      <c r="F27" s="14">
+        <v>300</v>
+      </c>
+      <c r="G27" s="14">
+        <v>6</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>100</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>200</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B29" s="14">
+        <v>450</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>100</v>
+      </c>
+      <c r="E29" s="14">
+        <v>50</v>
+      </c>
+      <c r="F29" s="14">
+        <v>250</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B30" s="14">
+        <v>480</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>50</v>
+      </c>
+      <c r="D32" s="14">
+        <v>100</v>
+      </c>
+      <c r="E32" s="14">
+        <v>40</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>920</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>520</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>100</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>350</v>
+      </c>
+      <c r="G33" s="14">
+        <v>7</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>100</v>
+      </c>
+      <c r="E34" s="14">
+        <v>40</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>6</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>50</v>
+      </c>
+      <c r="D35" s="14">
+        <v>60</v>
+      </c>
+      <c r="E35" s="14">
+        <v>40</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>50</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>60</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>530</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="14">
+        <v>480</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>120</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="14">
+        <v>480</v>
+      </c>
+      <c r="C38" s="14">
+        <v>60</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>120</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2683,11 +3126,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -2705,11 +3148,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -4091,11 +4534,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I133:I196" si="4">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4113,11 +4556,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5499,11 +5942,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I197:I260" si="6">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5521,11 +5964,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6907,11 +7350,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I261:I324" si="8">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6929,11 +7372,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -8315,11 +8758,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I325:I388" si="10">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8337,11 +8780,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9723,11 +10166,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I389:I400" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9745,11 +10188,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9977,28 +10420,6 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10008,21 +10429,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J400">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B485B08-C0A4-4A99-AD2E-DD221968CB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B7D9A8-34ED-4AE9-8A88-016DB4E22830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2457,135 +2457,267 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B39" s="14">
+        <v>420</v>
+      </c>
+      <c r="C39" s="14">
+        <v>30</v>
+      </c>
+      <c r="D39" s="14">
+        <v>120</v>
+      </c>
+      <c r="E39" s="14">
+        <v>60</v>
+      </c>
+      <c r="F39" s="14">
+        <v>250</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>60</v>
+      </c>
+      <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
+        <v>7</v>
+      </c>
+      <c r="H40" s="14">
+        <v>60</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B41" s="14">
+        <v>420</v>
+      </c>
+      <c r="C41" s="14">
+        <v>30</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>60</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>200</v>
+      </c>
+      <c r="G42" s="14">
+        <v>4</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>30</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>250</v>
+      </c>
+      <c r="G43" s="14">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14">
+        <v>60</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>60</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>750</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B7D9A8-34ED-4AE9-8A88-016DB4E22830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3536B596-DAE4-4B3F-9833-3814E17EB479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2721,47 +2721,91 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>60</v>
+      </c>
+      <c r="D45" s="14">
+        <v>120</v>
+      </c>
+      <c r="E45" s="14">
+        <v>60</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>60</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>660</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>100</v>
+      </c>
+      <c r="E46" s="14">
+        <v>45</v>
+      </c>
+      <c r="F46" s="14">
+        <v>250</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>60</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>535</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3536B596-DAE4-4B3F-9833-3814E17EB479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC022BDE-3B84-436E-8E18-2041CE343B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Vivek Kumar Barh</t>
   </si>
   <si>
-    <t>cap776</t>
-  </si>
-  <si>
     <t>august</t>
   </si>
   <si>
@@ -224,6 +221,9 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>cap776/D1P2636</t>
   </si>
 </sst>
 </file>
@@ -928,7 +928,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -936,7 +936,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1045,7 +1045,7 @@
         <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1088,7 +1088,7 @@
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N7" s="17"/>
     </row>
@@ -1129,7 +1129,7 @@
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>51</v>
@@ -1170,13 +1170,13 @@
         <v>610</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N9" s="17"/>
     </row>
@@ -1214,13 +1214,13 @@
         <v>630</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N10" s="17"/>
     </row>
@@ -1396,7 +1396,7 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N14" s="17"/>
     </row>
@@ -1440,7 +1440,7 @@
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1478,13 +1478,13 @@
         <v>680</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N16" s="17"/>
     </row>
@@ -1522,13 +1522,13 @@
         <v>660</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N17" s="17"/>
     </row>
@@ -1742,13 +1742,13 @@
         <v>720</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N22" s="17"/>
     </row>
@@ -1786,13 +1786,13 @@
         <v>720</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N23" s="17"/>
     </row>
@@ -1830,13 +1830,13 @@
         <v>720</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N24" s="17"/>
     </row>
@@ -1874,13 +1874,13 @@
         <v>720</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N25" s="17"/>
     </row>
@@ -2094,13 +2094,13 @@
         <v>600</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N30" s="17"/>
     </row>
@@ -2138,13 +2138,13 @@
         <v>600</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N31" s="17"/>
     </row>
@@ -2226,13 +2226,13 @@
         <v>450</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -2314,13 +2314,13 @@
         <v>590</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N35" s="17"/>
     </row>
@@ -2402,13 +2402,13 @@
         <v>600</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N37" s="17"/>
     </row>
@@ -2446,13 +2446,13 @@
         <v>600</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N38" s="17"/>
     </row>
@@ -2496,7 +2496,7 @@
         <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N39" s="17"/>
     </row>
@@ -2584,7 +2584,7 @@
         <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N41" s="17"/>
     </row>
@@ -2622,13 +2622,13 @@
         <v>550</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N42" s="17"/>
     </row>
@@ -2666,13 +2666,13 @@
         <v>500</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N43" s="17"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>750</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M44" s="16" t="s">
         <v>51</v>
@@ -2754,13 +2754,13 @@
         <v>660</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M45" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N45" s="17"/>
     </row>
@@ -2809,69 +2809,135 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>30</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>45</v>
+      </c>
+      <c r="F47" s="14">
+        <v>350</v>
+      </c>
+      <c r="G47" s="14">
+        <v>7</v>
+      </c>
+      <c r="H47" s="14">
+        <v>60</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>415</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B48" s="14">
+        <v>420</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14">
+        <v>120</v>
+      </c>
+      <c r="E48" s="14">
+        <v>45</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>60</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>975</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>465</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>45</v>
+      </c>
+      <c r="F49" s="14">
+        <v>150</v>
+      </c>
+      <c r="G49" s="14">
+        <v>3</v>
+      </c>
+      <c r="H49" s="14">
+        <v>60</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>825</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>615</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC022BDE-3B84-436E-8E18-2041CE343B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC1BBA0-F7A7-4236-AA34-5BBDBE103FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2941,25 +2941,47 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B50" s="14">
+        <v>420</v>
+      </c>
+      <c r="C50" s="14">
+        <v>45</v>
+      </c>
+      <c r="D50" s="14">
+        <v>100</v>
+      </c>
+      <c r="E50" s="14">
+        <v>120</v>
+      </c>
+      <c r="F50" s="14">
+        <v>250</v>
+      </c>
+      <c r="G50" s="14">
+        <v>5</v>
+      </c>
+      <c r="H50" s="14">
+        <v>60</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>445</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC1BBA0-F7A7-4236-AA34-5BBDBE103FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1B2C1E-1B76-4373-85D2-97FA7D66CA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2985,25 +2985,47 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B51" s="14">
+        <v>480</v>
+      </c>
+      <c r="C51" s="14">
+        <v>60</v>
+      </c>
+      <c r="D51" s="14">
+        <v>100</v>
+      </c>
+      <c r="E51" s="14">
+        <v>120</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>60</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1B2C1E-1B76-4373-85D2-97FA7D66CA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E4AF9-663C-4281-851A-DCA443EE847B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>High</t>
-  </si>
-  <si>
-    <t>satisfied</t>
   </si>
   <si>
     <t>Very Satisfied</t>
@@ -928,7 +925,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1129,7 +1126,7 @@
         <v>49</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>51</v>
@@ -1170,10 +1167,10 @@
         <v>610</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>56</v>
@@ -1214,10 +1211,10 @@
         <v>630</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M10" s="16" t="s">
         <v>56</v>
@@ -1440,7 +1437,7 @@
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1478,10 +1475,10 @@
         <v>680</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>56</v>
@@ -1522,10 +1519,10 @@
         <v>660</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M17" s="16" t="s">
         <v>56</v>
@@ -1742,10 +1739,10 @@
         <v>720</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>56</v>
@@ -1786,10 +1783,10 @@
         <v>720</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>56</v>
@@ -1830,10 +1827,10 @@
         <v>720</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M24" s="16" t="s">
         <v>56</v>
@@ -1874,10 +1871,10 @@
         <v>720</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>56</v>
@@ -2094,10 +2091,10 @@
         <v>600</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M30" s="16" t="s">
         <v>56</v>
@@ -2138,10 +2135,10 @@
         <v>600</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M31" s="16" t="s">
         <v>56</v>
@@ -2226,13 +2223,13 @@
         <v>450</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -2314,10 +2311,10 @@
         <v>590</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>56</v>
@@ -2402,10 +2399,10 @@
         <v>600</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M37" s="16" t="s">
         <v>56</v>
@@ -2446,10 +2443,10 @@
         <v>600</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M38" s="16" t="s">
         <v>56</v>
@@ -2622,10 +2619,10 @@
         <v>550</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M42" s="16" t="s">
         <v>56</v>
@@ -2666,10 +2663,10 @@
         <v>500</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M43" s="16" t="s">
         <v>56</v>
@@ -2710,10 +2707,10 @@
         <v>750</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L44" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M44" s="16" t="s">
         <v>51</v>
@@ -2754,10 +2751,10 @@
         <v>660</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L45" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M45" s="16" t="s">
         <v>56</v>
@@ -2886,13 +2883,13 @@
         <v>465</v>
       </c>
       <c r="K48" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L48" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M48" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N48" s="17"/>
     </row>
@@ -2930,7 +2927,7 @@
         <v>615</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L49" s="16" t="s">
         <v>50</v>
@@ -2974,7 +2971,7 @@
         <v>445</v>
       </c>
       <c r="K50" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L50" s="16" t="s">
         <v>50</v>
@@ -3018,10 +3015,10 @@
         <v>620</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L51" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M51" s="16" t="s">
         <v>56</v>

--- a/12601885.xlsx
+++ b/12601885.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cap776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E4AF9-663C-4281-851A-DCA443EE847B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEDDFBE-DA9D-49D2-952C-68234F5DB635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3026,157 +3026,311 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B52" s="14">
+        <v>480</v>
+      </c>
+      <c r="C52" s="14">
+        <v>60</v>
+      </c>
+      <c r="D52" s="14">
+        <v>120</v>
+      </c>
+      <c r="E52" s="14">
+        <v>120</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>60</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>600</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B53" s="14">
+        <v>480</v>
+      </c>
+      <c r="C53" s="14">
+        <v>60</v>
+      </c>
+      <c r="D53" s="14">
+        <v>100</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B54" s="14">
+        <v>480</v>
+      </c>
+      <c r="C54" s="14">
+        <v>60</v>
+      </c>
+      <c r="D54" s="14">
+        <v>100</v>
+      </c>
+      <c r="E54" s="14">
+        <v>60</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>120</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B55" s="14">
+        <v>480</v>
+      </c>
+      <c r="C55" s="14">
+        <v>60</v>
+      </c>
+      <c r="D55" s="14">
+        <v>100</v>
+      </c>
+      <c r="E55" s="14">
+        <v>60</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>120</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B56" s="14">
+        <v>480</v>
+      </c>
+      <c r="C56" s="14">
+        <v>60</v>
+      </c>
+      <c r="D56" s="14">
+        <v>100</v>
+      </c>
+      <c r="E56" s="14">
+        <v>60</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>120</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B57" s="14">
+        <v>480</v>
+      </c>
+      <c r="C57" s="14">
+        <v>60</v>
+      </c>
+      <c r="D57" s="14">
+        <v>100</v>
+      </c>
+      <c r="E57" s="14">
+        <v>60</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>120</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B58" s="14">
+        <v>480</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>100</v>
+      </c>
+      <c r="E58" s="14">
+        <v>60</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>120</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
+        <v>620</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
